--- a/tools/excel_export/excel/tasks.xlsx
+++ b/tools/excel_export/excel/tasks.xlsx
@@ -772,10 +772,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I4" s="4">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="J4" s="4">
         <v>1</v>
@@ -805,10 +805,10 @@
         <v>100</v>
       </c>
       <c r="H5" s="4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I5" s="4">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -838,10 +838,10 @@
         <v>3</v>
       </c>
       <c r="H6" s="4">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="I6" s="4">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="J6" s="4">
         <v>1</v>
@@ -871,10 +871,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I7" s="4">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="J7" s="4">
         <v>2</v>
@@ -904,10 +904,10 @@
         <v>10</v>
       </c>
       <c r="H8" s="4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I8" s="4">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="J8" s="4">
         <v>2</v>
@@ -937,10 +937,10 @@
         <v>500</v>
       </c>
       <c r="H9" s="4">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I9" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J9" s="4">
         <v>1</v>
@@ -970,10 +970,10 @@
         <v>20</v>
       </c>
       <c r="H10" s="4">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="I10" s="4">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J10" s="4">
         <v>1</v>
@@ -1003,10 +1003,10 @@
         <v>1500</v>
       </c>
       <c r="H11" s="4">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="I11" s="4">
-        <v>2000</v>
+        <v>650</v>
       </c>
       <c r="J11" s="4">
         <v>1</v>
@@ -1036,10 +1036,10 @@
         <v>4</v>
       </c>
       <c r="H12" s="4">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I12" s="4">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="J12" s="4">
         <v>1</v>
@@ -1069,10 +1069,10 @@
         <v>10</v>
       </c>
       <c r="H13" s="4">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I13" s="4">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="J13" s="4">
         <v>2</v>
@@ -1102,10 +1102,10 @@
         <v>2000</v>
       </c>
       <c r="H14" s="4">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="I14" s="4">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="J14" s="4">
         <v>2</v>
@@ -1135,10 +1135,10 @@
         <v>15</v>
       </c>
       <c r="H15" s="4">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="I15" s="4">
-        <v>2400</v>
+        <v>700</v>
       </c>
       <c r="J15" s="4">
         <v>3</v>
